--- a/2526.xlsx
+++ b/2526.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oapindia-my.sharepoint.com/personal/jesley_joseph_oapindia_com/Documents/docs/revenues/2526/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27CDB384-67A3-4D6C-A47D-483E96DA47B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B460B7-31C9-4ECB-8A84-34FD89350467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4356FD04-6C7D-4AD1-9A02-B0721BAA9E85}"/>
   </bookViews>
@@ -935,7 +935,9 @@
         <f t="shared" ref="L3:L38" si="1">+J3-K3</f>
         <v>6937</v>
       </c>
-      <c r="M3" s="11"/>
+      <c r="M3" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -974,7 +976,9 @@
         <f t="shared" si="1"/>
         <v>25000</v>
       </c>
-      <c r="M4" s="11"/>
+      <c r="M4" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1054,7 +1058,9 @@
         <f t="shared" si="1"/>
         <v>35400</v>
       </c>
-      <c r="M6" s="11"/>
+      <c r="M6" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1093,7 +1099,9 @@
         <f t="shared" si="1"/>
         <v>15307</v>
       </c>
-      <c r="M7" s="11"/>
+      <c r="M7" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1132,7 +1140,9 @@
         <f t="shared" si="1"/>
         <v>2400</v>
       </c>
-      <c r="M8" s="11"/>
+      <c r="M8" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1171,7 +1181,9 @@
         <f t="shared" si="1"/>
         <v>84000</v>
       </c>
-      <c r="M9" s="11"/>
+      <c r="M9" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1210,7 +1222,9 @@
         <f t="shared" si="1"/>
         <v>34000</v>
       </c>
-      <c r="M10" s="11"/>
+      <c r="M10" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1290,7 +1304,9 @@
         <f t="shared" si="1"/>
         <v>518733</v>
       </c>
-      <c r="M12" s="11"/>
+      <c r="M12" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1329,7 +1345,9 @@
         <f t="shared" si="1"/>
         <v>600000</v>
       </c>
-      <c r="M13" s="11"/>
+      <c r="M13" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1368,7 +1386,9 @@
         <f t="shared" si="1"/>
         <v>276292</v>
       </c>
-      <c r="M14" s="11"/>
+      <c r="M14" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1407,7 +1427,9 @@
         <f t="shared" si="1"/>
         <v>473900</v>
       </c>
-      <c r="M15" s="11"/>
+      <c r="M15" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1446,7 +1468,9 @@
         <f t="shared" si="1"/>
         <v>210030</v>
       </c>
-      <c r="M16" s="11"/>
+      <c r="M16" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -1485,7 +1509,9 @@
         <f t="shared" si="1"/>
         <v>166500</v>
       </c>
-      <c r="M17" s="11"/>
+      <c r="M17" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -1524,7 +1550,9 @@
         <f t="shared" si="1"/>
         <v>157600</v>
       </c>
-      <c r="M18" s="11"/>
+      <c r="M18" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -1563,7 +1591,9 @@
         <f t="shared" si="1"/>
         <v>4800</v>
       </c>
-      <c r="M19" s="11"/>
+      <c r="M19" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -1602,7 +1632,9 @@
         <f t="shared" si="1"/>
         <v>27300</v>
       </c>
-      <c r="M20" s="11"/>
+      <c r="M20" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
@@ -1641,7 +1673,9 @@
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="M21" s="11"/>
+      <c r="M21" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -1681,7 +1715,9 @@
         <f t="shared" si="1"/>
         <v>13100</v>
       </c>
-      <c r="M22" s="11"/>
+      <c r="M22" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -1720,7 +1756,9 @@
         <f t="shared" si="1"/>
         <v>14733</v>
       </c>
-      <c r="M23" s="11"/>
+      <c r="M23" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -1759,7 +1797,9 @@
         <f t="shared" si="1"/>
         <v>18900</v>
       </c>
-      <c r="M24" s="11"/>
+      <c r="M24" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -1798,7 +1838,9 @@
         <f t="shared" si="1"/>
         <v>4000</v>
       </c>
-      <c r="M25" s="11"/>
+      <c r="M25" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -1837,7 +1879,9 @@
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
-      <c r="M26" s="11"/>
+      <c r="M26" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -1876,7 +1920,9 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="M27" s="11"/>
+      <c r="M27" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
@@ -1915,7 +1961,9 @@
         <f t="shared" si="1"/>
         <v>5450</v>
       </c>
-      <c r="M28" s="11"/>
+      <c r="M28" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -1954,7 +2002,9 @@
         <f t="shared" si="1"/>
         <v>468850</v>
       </c>
-      <c r="M29" s="11"/>
+      <c r="M29" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
@@ -1993,7 +2043,9 @@
         <f t="shared" si="1"/>
         <v>28000</v>
       </c>
-      <c r="M30" s="11"/>
+      <c r="M30" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -2032,7 +2084,9 @@
         <f t="shared" si="1"/>
         <v>17395</v>
       </c>
-      <c r="M31" s="11"/>
+      <c r="M31" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -2071,7 +2125,9 @@
         <f t="shared" si="1"/>
         <v>90910</v>
       </c>
-      <c r="M32" s="11"/>
+      <c r="M32" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
@@ -2110,7 +2166,9 @@
         <f t="shared" si="1"/>
         <v>2400</v>
       </c>
-      <c r="M33" s="11"/>
+      <c r="M33" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
@@ -2149,7 +2207,9 @@
         <f t="shared" si="1"/>
         <v>1875</v>
       </c>
-      <c r="M34" s="11"/>
+      <c r="M34" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
@@ -2188,7 +2248,9 @@
         <f t="shared" si="1"/>
         <v>2352</v>
       </c>
-      <c r="M35" s="11"/>
+      <c r="M35" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
@@ -2227,7 +2289,9 @@
         <f t="shared" si="1"/>
         <v>50000</v>
       </c>
-      <c r="M36" s="11"/>
+      <c r="M36" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
@@ -2264,7 +2328,9 @@
         <f t="shared" si="1"/>
         <v>38400</v>
       </c>
-      <c r="M37" s="11"/>
+      <c r="M37" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
@@ -2303,7 +2369,9 @@
         <f t="shared" si="1"/>
         <v>43200</v>
       </c>
-      <c r="M38" s="11"/>
+      <c r="M38" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="39" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
@@ -2335,7 +2403,9 @@
       <c r="L39" s="8">
         <v>437000</v>
       </c>
-      <c r="M39" s="11"/>
+      <c r="M39" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
@@ -2367,7 +2437,9 @@
       <c r="L40" s="8">
         <v>2400</v>
       </c>
-      <c r="M40" s="11"/>
+      <c r="M40" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
@@ -2399,7 +2471,9 @@
       <c r="L41" s="8">
         <v>4400</v>
       </c>
-      <c r="M41" s="11"/>
+      <c r="M41" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
@@ -2431,7 +2505,9 @@
       <c r="L42" s="8">
         <v>4800</v>
       </c>
-      <c r="M42" s="11"/>
+      <c r="M42" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
@@ -2463,7 +2539,9 @@
       <c r="L43" s="8">
         <v>2700</v>
       </c>
-      <c r="M43" s="11"/>
+      <c r="M43" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
@@ -2495,7 +2573,9 @@
       <c r="L44" s="8">
         <v>34201</v>
       </c>
-      <c r="M44" s="11"/>
+      <c r="M44" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
@@ -2527,7 +2607,9 @@
       <c r="L45" s="8">
         <v>13351</v>
       </c>
-      <c r="M45" s="11"/>
+      <c r="M45" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="46" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
@@ -2559,7 +2641,9 @@
       <c r="L46" s="8">
         <v>62405</v>
       </c>
-      <c r="M46" s="11"/>
+      <c r="M46" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="47" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
@@ -2591,7 +2675,9 @@
       <c r="L47" s="8">
         <v>-29099</v>
       </c>
-      <c r="M47" s="11"/>
+      <c r="M47" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="48" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
@@ -2623,7 +2709,9 @@
       <c r="L48" s="8">
         <v>77499</v>
       </c>
-      <c r="M48" s="11"/>
+      <c r="M48" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="49" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
@@ -2689,7 +2777,9 @@
       <c r="L50" s="8">
         <v>44200</v>
       </c>
-      <c r="M50" s="11"/>
+      <c r="M50" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="51" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
@@ -2721,7 +2811,9 @@
       <c r="L51" s="8">
         <v>13208</v>
       </c>
-      <c r="M51" s="11"/>
+      <c r="M51" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
@@ -2753,7 +2845,9 @@
       <c r="L52" s="8">
         <v>-117266</v>
       </c>
-      <c r="M52" s="11"/>
+      <c r="M52" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
@@ -2785,7 +2879,9 @@
       <c r="L53" s="8">
         <v>129167</v>
       </c>
-      <c r="M53" s="11"/>
+      <c r="M53" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
@@ -2906,7 +3002,9 @@
         <f t="shared" si="2"/>
         <v>1250</v>
       </c>
-      <c r="M56" s="11"/>
+      <c r="M56" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -2945,7 +3043,9 @@
         <f t="shared" si="2"/>
         <v>83333</v>
       </c>
-      <c r="M57" s="11"/>
+      <c r="M57" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
@@ -2984,7 +3084,9 @@
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
-      <c r="M58" s="11"/>
+      <c r="M58" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
@@ -3023,7 +3125,9 @@
         <f t="shared" si="2"/>
         <v>5900</v>
       </c>
-      <c r="M59" s="11"/>
+      <c r="M59" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
@@ -3062,7 +3166,9 @@
         <f t="shared" si="2"/>
         <v>5467</v>
       </c>
-      <c r="M60" s="11"/>
+      <c r="M60" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
@@ -3101,7 +3207,9 @@
         <f t="shared" si="2"/>
         <v>8625</v>
       </c>
-      <c r="M61" s="11"/>
+      <c r="M61" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="62" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
@@ -3140,7 +3248,9 @@
         <f t="shared" si="2"/>
         <v>3539</v>
       </c>
-      <c r="M62" s="11"/>
+      <c r="M62" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
@@ -3179,7 +3289,9 @@
         <f t="shared" si="2"/>
         <v>150000</v>
       </c>
-      <c r="M63" s="11"/>
+      <c r="M63" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
@@ -3218,7 +3330,9 @@
         <f t="shared" si="2"/>
         <v>183900</v>
       </c>
-      <c r="M64" s="11"/>
+      <c r="M64" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
@@ -3257,7 +3371,9 @@
         <f t="shared" si="2"/>
         <v>457650</v>
       </c>
-      <c r="M65" s="11"/>
+      <c r="M65" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="66" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
@@ -3296,7 +3412,9 @@
         <f t="shared" si="2"/>
         <v>52000</v>
       </c>
-      <c r="M66" s="11"/>
+      <c r="M66" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
@@ -3335,7 +3453,9 @@
         <f t="shared" si="2"/>
         <v>32775</v>
       </c>
-      <c r="M67" s="11"/>
+      <c r="M67" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="68" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
@@ -3374,7 +3494,9 @@
         <f t="shared" si="2"/>
         <v>30075</v>
       </c>
-      <c r="M68" s="11"/>
+      <c r="M68" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="69" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
@@ -3454,7 +3576,9 @@
         <f t="shared" si="2"/>
         <v>18880</v>
       </c>
-      <c r="M70" s="11"/>
+      <c r="M70" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
@@ -3493,7 +3617,9 @@
         <f t="shared" si="2"/>
         <v>9800</v>
       </c>
-      <c r="M71" s="11"/>
+      <c r="M71" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="72" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
@@ -3532,7 +3658,9 @@
         <f t="shared" si="2"/>
         <v>30666</v>
       </c>
-      <c r="M72" s="11"/>
+      <c r="M72" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="73" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
@@ -3571,7 +3699,9 @@
         <f t="shared" si="2"/>
         <v>9000</v>
       </c>
-      <c r="M73" s="11"/>
+      <c r="M73" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="74" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
@@ -3610,7 +3740,9 @@
         <f t="shared" si="2"/>
         <v>12200</v>
       </c>
-      <c r="M74" s="11"/>
+      <c r="M74" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="75" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
@@ -3649,7 +3781,9 @@
         <f t="shared" si="2"/>
         <v>180000</v>
       </c>
-      <c r="M75" s="11"/>
+      <c r="M75" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="76" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
@@ -3688,7 +3822,9 @@
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="M76" s="11"/>
+      <c r="M76" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="77" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
@@ -3727,7 +3863,9 @@
         <f t="shared" si="2"/>
         <v>452370</v>
       </c>
-      <c r="M77" s="11"/>
+      <c r="M77" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="78" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
@@ -3766,7 +3904,9 @@
         <f t="shared" si="2"/>
         <v>96580</v>
       </c>
-      <c r="M78" s="11"/>
+      <c r="M78" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="79" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
@@ -3805,7 +3945,9 @@
         <f t="shared" si="2"/>
         <v>25360</v>
       </c>
-      <c r="M79" s="11"/>
+      <c r="M79" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="80" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
@@ -3842,7 +3984,9 @@
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M80" s="11"/>
+      <c r="M80" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="81" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
@@ -3922,7 +4066,9 @@
         <f t="shared" si="2"/>
         <v>110000</v>
       </c>
-      <c r="M82" s="11"/>
+      <c r="M82" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="83" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
@@ -3961,7 +4107,9 @@
         <f t="shared" si="2"/>
         <v>30000</v>
       </c>
-      <c r="M83" s="11"/>
+      <c r="M83" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="84" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
@@ -4082,7 +4230,9 @@
         <f t="shared" si="2"/>
         <v>9720</v>
       </c>
-      <c r="M86" s="11"/>
+      <c r="M86" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="87" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
@@ -4121,7 +4271,9 @@
         <f t="shared" si="2"/>
         <v>15800</v>
       </c>
-      <c r="M87" s="11"/>
+      <c r="M87" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="88" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
@@ -4160,7 +4312,9 @@
         <f t="shared" si="2"/>
         <v>80000</v>
       </c>
-      <c r="M88" s="11"/>
+      <c r="M88" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="89" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
@@ -4199,7 +4353,9 @@
         <f t="shared" si="2"/>
         <v>481947</v>
       </c>
-      <c r="M89" s="11"/>
+      <c r="M89" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="90" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
@@ -4238,7 +4394,9 @@
         <f t="shared" si="2"/>
         <v>16250</v>
       </c>
-      <c r="M90" s="11"/>
+      <c r="M90" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
@@ -4277,7 +4435,9 @@
         <f t="shared" si="2"/>
         <v>3750</v>
       </c>
-      <c r="M91" s="11"/>
+      <c r="M91" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="92" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
@@ -4357,7 +4517,9 @@
         <f t="shared" si="2"/>
         <v>18168</v>
       </c>
-      <c r="M93" s="11"/>
+      <c r="M93" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="94" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
@@ -4396,7 +4558,9 @@
         <f t="shared" si="2"/>
         <v>5900</v>
       </c>
-      <c r="M94" s="11"/>
+      <c r="M94" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="95" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
@@ -4435,7 +4599,9 @@
         <f t="shared" si="2"/>
         <v>6937</v>
       </c>
-      <c r="M95" s="11"/>
+      <c r="M95" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="96" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
@@ -4474,7 +4640,9 @@
         <f t="shared" si="2"/>
         <v>36000</v>
       </c>
-      <c r="M96" s="11"/>
+      <c r="M96" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="97" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
@@ -4513,7 +4681,9 @@
         <f t="shared" si="2"/>
         <v>4000</v>
       </c>
-      <c r="M97" s="11"/>
+      <c r="M97" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="98" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
@@ -4552,7 +4722,9 @@
         <f t="shared" si="2"/>
         <v>23625</v>
       </c>
-      <c r="M98" s="11"/>
+      <c r="M98" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="99" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
@@ -4591,7 +4763,9 @@
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M99" s="11"/>
+      <c r="M99" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="100" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
@@ -4630,7 +4804,9 @@
         <f t="shared" si="2"/>
         <v>4000</v>
       </c>
-      <c r="M100" s="11"/>
+      <c r="M100" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
@@ -4669,7 +4845,9 @@
         <f t="shared" si="2"/>
         <v>100000</v>
       </c>
-      <c r="M101" s="11"/>
+      <c r="M101" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="102" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
@@ -4708,7 +4886,9 @@
         <f t="shared" si="2"/>
         <v>24400</v>
       </c>
-      <c r="M102" s="11"/>
+      <c r="M102" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="103" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
@@ -4747,7 +4927,9 @@
         <f t="shared" si="2"/>
         <v>148813</v>
       </c>
-      <c r="M103" s="11"/>
+      <c r="M103" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="104" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
@@ -4786,7 +4968,9 @@
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="M104" s="11"/>
+      <c r="M104" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="105" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
@@ -4825,7 +5009,9 @@
         <f t="shared" si="2"/>
         <v>10000</v>
       </c>
-      <c r="M105" s="11"/>
+      <c r="M105" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="106" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
@@ -4864,7 +5050,9 @@
         <f t="shared" si="2"/>
         <v>4200</v>
       </c>
-      <c r="M106" s="11"/>
+      <c r="M106" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="107" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
@@ -4903,7 +5091,9 @@
         <f t="shared" si="2"/>
         <v>10500</v>
       </c>
-      <c r="M107" s="11"/>
+      <c r="M107" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="108" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
@@ -4942,7 +5132,9 @@
         <f t="shared" si="2"/>
         <v>54375</v>
       </c>
-      <c r="M108" s="11"/>
+      <c r="M108" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="109" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
@@ -4981,7 +5173,9 @@
         <f t="shared" si="2"/>
         <v>15487</v>
       </c>
-      <c r="M109" s="11"/>
+      <c r="M109" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="110" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
@@ -5020,7 +5214,9 @@
         <f t="shared" si="2"/>
         <v>19687</v>
       </c>
-      <c r="M110" s="11"/>
+      <c r="M110" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="111" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
@@ -5059,7 +5255,9 @@
         <f t="shared" si="2"/>
         <v>25300</v>
       </c>
-      <c r="M111" s="11"/>
+      <c r="M111" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="112" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -5098,7 +5296,9 @@
         <f t="shared" si="2"/>
         <v>7017</v>
       </c>
-      <c r="M112" s="11"/>
+      <c r="M112" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="113" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
@@ -5137,7 +5337,9 @@
         <f t="shared" si="2"/>
         <v>25720</v>
       </c>
-      <c r="M113" s="11"/>
+      <c r="M113" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="114" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
@@ -5176,7 +5378,9 @@
         <f t="shared" si="2"/>
         <v>23500</v>
       </c>
-      <c r="M114" s="11"/>
+      <c r="M114" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="115" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
@@ -5215,7 +5419,9 @@
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="M115" s="11"/>
+      <c r="M115" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="116" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
@@ -5254,7 +5460,9 @@
         <f t="shared" si="2"/>
         <v>12250</v>
       </c>
-      <c r="M116" s="11"/>
+      <c r="M116" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="117" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
@@ -5293,7 +5501,9 @@
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M117" s="11"/>
+      <c r="M117" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="118" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
@@ -5332,7 +5542,9 @@
         <f t="shared" ref="L118:L131" si="4">+J118-K118</f>
         <v>20000</v>
       </c>
-      <c r="M118" s="11"/>
+      <c r="M118" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="119" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
@@ -5371,7 +5583,9 @@
         <f t="shared" si="4"/>
         <v>16200</v>
       </c>
-      <c r="M119" s="11"/>
+      <c r="M119" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="120" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
@@ -5410,7 +5624,9 @@
         <f t="shared" si="4"/>
         <v>14500</v>
       </c>
-      <c r="M120" s="11"/>
+      <c r="M120" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="121" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
@@ -5447,7 +5663,9 @@
         <f t="shared" si="4"/>
         <v>19200</v>
       </c>
-      <c r="M121" s="11"/>
+      <c r="M121" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="122" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
@@ -5486,7 +5704,9 @@
         <f t="shared" si="4"/>
         <v>57000</v>
       </c>
-      <c r="M122" s="11"/>
+      <c r="M122" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="123" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
@@ -5525,7 +5745,9 @@
         <f t="shared" si="4"/>
         <v>13600</v>
       </c>
-      <c r="M123" s="11"/>
+      <c r="M123" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="124" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
@@ -5564,7 +5786,9 @@
         <f t="shared" si="4"/>
         <v>3200</v>
       </c>
-      <c r="M124" s="11"/>
+      <c r="M124" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="125" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
@@ -5603,7 +5827,9 @@
         <f t="shared" si="4"/>
         <v>300000</v>
       </c>
-      <c r="M125" s="11"/>
+      <c r="M125" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="126" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
@@ -5642,7 +5868,9 @@
         <f t="shared" si="4"/>
         <v>3750</v>
       </c>
-      <c r="M126" s="11"/>
+      <c r="M126" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="127" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
@@ -5722,7 +5950,9 @@
         <f t="shared" si="4"/>
         <v>50000</v>
       </c>
-      <c r="M128" s="11"/>
+      <c r="M128" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="129" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
@@ -5761,7 +5991,9 @@
         <f t="shared" si="4"/>
         <v>32400</v>
       </c>
-      <c r="M129" s="11"/>
+      <c r="M129" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="130" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
@@ -5800,7 +6032,9 @@
         <f t="shared" si="4"/>
         <v>589982</v>
       </c>
-      <c r="M130" s="11"/>
+      <c r="M130" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="131" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
@@ -5839,7 +6073,9 @@
         <f t="shared" si="4"/>
         <v>103333</v>
       </c>
-      <c r="M131" s="11"/>
+      <c r="M131" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="132" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
@@ -5871,7 +6107,9 @@
       <c r="L132" s="8">
         <v>32625</v>
       </c>
-      <c r="M132" s="11"/>
+      <c r="M132" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="133" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
@@ -5910,7 +6148,9 @@
         <f t="shared" ref="L133:L197" si="6">+J133-K133</f>
         <v>8580</v>
       </c>
-      <c r="M133" s="11"/>
+      <c r="M133" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="134" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
@@ -5949,7 +6189,9 @@
         <f t="shared" si="6"/>
         <v>7830</v>
       </c>
-      <c r="M134" s="11"/>
+      <c r="M134" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="135" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
@@ -5988,7 +6230,9 @@
         <f t="shared" si="6"/>
         <v>4830</v>
       </c>
-      <c r="M135" s="11"/>
+      <c r="M135" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="136" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
@@ -6027,7 +6271,9 @@
         <f t="shared" si="6"/>
         <v>4830</v>
       </c>
-      <c r="M136" s="11"/>
+      <c r="M136" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="137" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
@@ -6066,7 +6312,9 @@
         <f t="shared" si="6"/>
         <v>4830</v>
       </c>
-      <c r="M137" s="11"/>
+      <c r="M137" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="138" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
@@ -6146,7 +6394,9 @@
         <f t="shared" si="6"/>
         <v>27117</v>
       </c>
-      <c r="M139" s="11"/>
+      <c r="M139" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="140" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
@@ -6183,7 +6433,9 @@
         <f t="shared" si="6"/>
         <v>15000</v>
       </c>
-      <c r="M140" s="11"/>
+      <c r="M140" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="141" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
@@ -6222,7 +6474,9 @@
         <f t="shared" si="6"/>
         <v>30000</v>
       </c>
-      <c r="M141" s="11"/>
+      <c r="M141" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="142" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
@@ -6302,7 +6556,9 @@
         <f t="shared" si="6"/>
         <v>6937</v>
       </c>
-      <c r="M143" s="11"/>
+      <c r="M143" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="144" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
@@ -6341,7 +6597,9 @@
         <f t="shared" si="6"/>
         <v>4333</v>
       </c>
-      <c r="M144" s="11"/>
+      <c r="M144" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="145" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
@@ -6380,7 +6638,9 @@
         <f t="shared" si="6"/>
         <v>150360</v>
       </c>
-      <c r="M145" s="11"/>
+      <c r="M145" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="146" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
@@ -6419,7 +6679,9 @@
         <f t="shared" si="6"/>
         <v>7000</v>
       </c>
-      <c r="M146" s="11"/>
+      <c r="M146" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="147" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
@@ -6458,7 +6720,9 @@
         <f t="shared" si="6"/>
         <v>27200</v>
       </c>
-      <c r="M147" s="11"/>
+      <c r="M147" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="148" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
@@ -6497,7 +6761,9 @@
         <f t="shared" si="6"/>
         <v>27680</v>
       </c>
-      <c r="M148" s="11"/>
+      <c r="M148" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="149" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
@@ -6536,7 +6802,9 @@
         <f t="shared" si="6"/>
         <v>50000</v>
       </c>
-      <c r="M149" s="11"/>
+      <c r="M149" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="150" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
@@ -6575,7 +6843,9 @@
         <f t="shared" si="6"/>
         <v>21841</v>
       </c>
-      <c r="M150" s="11"/>
+      <c r="M150" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="151" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
@@ -6614,7 +6884,9 @@
         <f t="shared" si="6"/>
         <v>325000</v>
       </c>
-      <c r="M151" s="11"/>
+      <c r="M151" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="152" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
@@ -6653,7 +6925,9 @@
         <f t="shared" si="6"/>
         <v>600000</v>
       </c>
-      <c r="M152" s="11"/>
+      <c r="M152" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="153" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
@@ -6692,7 +6966,9 @@
         <f t="shared" si="6"/>
         <v>300000</v>
       </c>
-      <c r="M153" s="11"/>
+      <c r="M153" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="154" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
@@ -6731,7 +7007,9 @@
         <f t="shared" si="6"/>
         <v>7880</v>
       </c>
-      <c r="M154" s="11"/>
+      <c r="M154" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="155" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
@@ -6770,7 +7048,9 @@
         <f t="shared" si="6"/>
         <v>235800</v>
       </c>
-      <c r="M155" s="11"/>
+      <c r="M155" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="156" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
@@ -6809,7 +7089,9 @@
         <f t="shared" si="6"/>
         <v>97980</v>
       </c>
-      <c r="M156" s="11"/>
+      <c r="M156" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="157" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
@@ -6889,7 +7171,9 @@
         <f t="shared" si="6"/>
         <v>35625</v>
       </c>
-      <c r="M158" s="11"/>
+      <c r="M158" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="159" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
@@ -6928,7 +7212,9 @@
         <f t="shared" si="6"/>
         <v>41150</v>
       </c>
-      <c r="M159" s="11"/>
+      <c r="M159" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="160" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
@@ -6967,7 +7253,9 @@
         <f t="shared" si="6"/>
         <v>42420</v>
       </c>
-      <c r="M160" s="11"/>
+      <c r="M160" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="161" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
@@ -7006,7 +7294,9 @@
         <f t="shared" si="6"/>
         <v>27090</v>
       </c>
-      <c r="M161" s="11"/>
+      <c r="M161" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="162" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
@@ -7045,7 +7335,9 @@
         <f t="shared" si="6"/>
         <v>676</v>
       </c>
-      <c r="M162" s="11"/>
+      <c r="M162" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="163" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
@@ -7084,7 +7376,9 @@
         <f t="shared" si="6"/>
         <v>9166</v>
       </c>
-      <c r="M163" s="11"/>
+      <c r="M163" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="164" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
@@ -7123,7 +7417,9 @@
         <f t="shared" si="6"/>
         <v>6666</v>
       </c>
-      <c r="M164" s="11"/>
+      <c r="M164" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="165" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
@@ -7162,7 +7458,9 @@
         <f t="shared" si="6"/>
         <v>7000</v>
       </c>
-      <c r="M165" s="11"/>
+      <c r="M165" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="166" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
@@ -7201,7 +7499,9 @@
         <f t="shared" si="6"/>
         <v>12000</v>
       </c>
-      <c r="M166" s="11"/>
+      <c r="M166" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="167" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
@@ -7240,7 +7540,9 @@
         <f t="shared" si="6"/>
         <v>10000</v>
       </c>
-      <c r="M167" s="11"/>
+      <c r="M167" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="168" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
@@ -7279,7 +7581,9 @@
         <f t="shared" si="6"/>
         <v>10000</v>
       </c>
-      <c r="M168" s="11"/>
+      <c r="M168" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="169" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
@@ -7318,7 +7622,9 @@
         <f t="shared" si="6"/>
         <v>95100</v>
       </c>
-      <c r="M169" s="11"/>
+      <c r="M169" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="170" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
@@ -7357,7 +7663,9 @@
         <f t="shared" si="6"/>
         <v>14500</v>
       </c>
-      <c r="M170" s="11"/>
+      <c r="M170" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="171" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
@@ -7396,7 +7704,9 @@
         <f t="shared" si="6"/>
         <v>165730</v>
       </c>
-      <c r="M171" s="11"/>
+      <c r="M171" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="172" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
@@ -7433,7 +7743,9 @@
         <f t="shared" si="6"/>
         <v>90400</v>
       </c>
-      <c r="M172" s="11"/>
+      <c r="M172" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="173" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
@@ -7472,7 +7784,9 @@
         <f t="shared" si="6"/>
         <v>160265</v>
       </c>
-      <c r="M173" s="11"/>
+      <c r="M173" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="174" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
@@ -7511,7 +7825,9 @@
         <f t="shared" si="6"/>
         <v>15000</v>
       </c>
-      <c r="M174" s="11"/>
+      <c r="M174" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="175" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
@@ -7550,7 +7866,9 @@
         <f t="shared" si="6"/>
         <v>84500</v>
       </c>
-      <c r="M175" s="11"/>
+      <c r="M175" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="176" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
@@ -7589,7 +7907,9 @@
         <f t="shared" si="6"/>
         <v>27425</v>
       </c>
-      <c r="M176" s="11"/>
+      <c r="M176" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="177" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
@@ -7628,7 +7948,9 @@
         <f t="shared" si="6"/>
         <v>3500</v>
       </c>
-      <c r="M177" s="11"/>
+      <c r="M177" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="178" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
@@ -7667,7 +7989,9 @@
         <f t="shared" si="6"/>
         <v>20000</v>
       </c>
-      <c r="M178" s="11"/>
+      <c r="M178" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="179" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
@@ -7747,7 +8071,9 @@
         <f t="shared" si="6"/>
         <v>81500</v>
       </c>
-      <c r="M180" s="11"/>
+      <c r="M180" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="181" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
@@ -7786,7 +8112,9 @@
         <f t="shared" si="6"/>
         <v>48900</v>
       </c>
-      <c r="M181" s="11"/>
+      <c r="M181" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="182" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
@@ -7825,7 +8153,9 @@
         <f t="shared" si="6"/>
         <v>10320</v>
       </c>
-      <c r="M182" s="11"/>
+      <c r="M182" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="183" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
@@ -7862,7 +8192,9 @@
         <f t="shared" si="6"/>
         <v>224580</v>
       </c>
-      <c r="M183" s="11"/>
+      <c r="M183" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="184" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
@@ -7901,7 +8233,9 @@
         <f t="shared" si="6"/>
         <v>50000</v>
       </c>
-      <c r="M184" s="11"/>
+      <c r="M184" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="185" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
@@ -8050,7 +8384,9 @@
         <f t="shared" si="6"/>
         <v>100000</v>
       </c>
-      <c r="M188" s="11"/>
+      <c r="M188" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="189" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
@@ -8089,7 +8425,9 @@
         <f t="shared" si="6"/>
         <v>5900</v>
       </c>
-      <c r="M189" s="11"/>
+      <c r="M189" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="190" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
@@ -8128,7 +8466,9 @@
         <f t="shared" si="6"/>
         <v>6937</v>
       </c>
-      <c r="M190" s="11"/>
+      <c r="M190" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="191" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
@@ -8165,7 +8505,9 @@
         <f t="shared" si="6"/>
         <v>15000</v>
       </c>
-      <c r="M191" s="10"/>
+      <c r="M191" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="192" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
@@ -8204,7 +8546,9 @@
         <f t="shared" si="6"/>
         <v>20000</v>
       </c>
-      <c r="M192" s="11"/>
+      <c r="M192" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="193" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
@@ -8243,7 +8587,9 @@
         <f t="shared" si="6"/>
         <v>22000</v>
       </c>
-      <c r="M193" s="11"/>
+      <c r="M193" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="194" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
@@ -8282,7 +8628,9 @@
         <f t="shared" si="6"/>
         <v>7000</v>
       </c>
-      <c r="M194" s="11"/>
+      <c r="M194" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="195" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
@@ -8321,7 +8669,9 @@
         <f t="shared" si="6"/>
         <v>140000</v>
       </c>
-      <c r="M195" s="11"/>
+      <c r="M195" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="196" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
@@ -8360,7 +8710,9 @@
         <f t="shared" si="6"/>
         <v>20000</v>
       </c>
-      <c r="M196" s="11"/>
+      <c r="M196" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="197" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
@@ -8399,7 +8751,9 @@
         <f t="shared" si="6"/>
         <v>2400</v>
       </c>
-      <c r="M197" s="11"/>
+      <c r="M197" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="198" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
@@ -8438,7 +8792,9 @@
         <f t="shared" ref="L198:L262" si="8">+J198-K198</f>
         <v>44502</v>
       </c>
-      <c r="M198" s="11"/>
+      <c r="M198" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="199" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
@@ -8477,7 +8833,9 @@
         <f t="shared" si="8"/>
         <v>24000</v>
       </c>
-      <c r="M199" s="11"/>
+      <c r="M199" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="200" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
@@ -8516,7 +8874,9 @@
         <f t="shared" si="8"/>
         <v>6000</v>
       </c>
-      <c r="M200" s="11"/>
+      <c r="M200" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="201" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
@@ -8555,7 +8915,9 @@
         <f t="shared" si="8"/>
         <v>12000</v>
       </c>
-      <c r="M201" s="11"/>
+      <c r="M201" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="202" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
@@ -8594,7 +8956,9 @@
         <f t="shared" si="8"/>
         <v>400</v>
       </c>
-      <c r="M202" s="11"/>
+      <c r="M202" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="203" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
@@ -8633,7 +8997,9 @@
         <f t="shared" si="8"/>
         <v>10900</v>
       </c>
-      <c r="M203" s="11"/>
+      <c r="M203" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="204" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
@@ -8672,7 +9038,9 @@
         <f t="shared" si="8"/>
         <v>11240</v>
       </c>
-      <c r="M204" s="11"/>
+      <c r="M204" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="205" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
@@ -8711,7 +9079,9 @@
         <f t="shared" si="8"/>
         <v>25000</v>
       </c>
-      <c r="M205" s="11"/>
+      <c r="M205" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="206" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
@@ -8750,7 +9120,9 @@
         <f t="shared" si="8"/>
         <v>20000</v>
       </c>
-      <c r="M206" s="11"/>
+      <c r="M206" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="207" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
@@ -8789,7 +9161,9 @@
         <f t="shared" si="8"/>
         <v>10000</v>
       </c>
-      <c r="M207" s="11"/>
+      <c r="M207" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="208" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
@@ -8828,7 +9202,9 @@
         <f t="shared" si="8"/>
         <v>10000</v>
       </c>
-      <c r="M208" s="11"/>
+      <c r="M208" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="209" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
@@ -8867,7 +9243,9 @@
         <f t="shared" si="8"/>
         <v>6000</v>
       </c>
-      <c r="M209" s="11"/>
+      <c r="M209" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="210" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
@@ -8906,7 +9284,9 @@
         <f t="shared" si="8"/>
         <v>18500</v>
       </c>
-      <c r="M210" s="11"/>
+      <c r="M210" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="211" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
@@ -8945,7 +9325,9 @@
         <f t="shared" si="8"/>
         <v>25008</v>
       </c>
-      <c r="M211" s="11"/>
+      <c r="M211" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="212" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
@@ -8984,7 +9366,9 @@
         <f t="shared" si="8"/>
         <v>50000</v>
       </c>
-      <c r="M212" s="11"/>
+      <c r="M212" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="213" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
@@ -9023,7 +9407,9 @@
         <f t="shared" si="8"/>
         <v>25000</v>
       </c>
-      <c r="M213" s="11"/>
+      <c r="M213" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="214" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
@@ -9062,7 +9448,9 @@
         <f t="shared" si="8"/>
         <v>16000</v>
       </c>
-      <c r="M214" s="11"/>
+      <c r="M214" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="215" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
@@ -9101,7 +9489,9 @@
         <f t="shared" si="8"/>
         <v>40000</v>
       </c>
-      <c r="M215" s="11"/>
+      <c r="M215" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="216" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
@@ -9140,7 +9530,9 @@
         <f t="shared" si="8"/>
         <v>30000</v>
       </c>
-      <c r="M216" s="11"/>
+      <c r="M216" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="217" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
@@ -9179,7 +9571,9 @@
         <f t="shared" si="8"/>
         <v>15000</v>
       </c>
-      <c r="M217" s="11"/>
+      <c r="M217" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="218" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
@@ -9218,7 +9612,9 @@
         <f t="shared" si="8"/>
         <v>90000</v>
       </c>
-      <c r="M218" s="11"/>
+      <c r="M218" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="219" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
@@ -9257,7 +9653,9 @@
         <f t="shared" si="8"/>
         <v>90000</v>
       </c>
-      <c r="M219" s="11"/>
+      <c r="M219" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="220" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
@@ -9290,7 +9688,9 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M220" s="11"/>
+      <c r="M220" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="221" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
@@ -9370,7 +9770,9 @@
         <f t="shared" si="8"/>
         <v>392000</v>
       </c>
-      <c r="M222" s="11"/>
+      <c r="M222" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="223" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
@@ -9409,7 +9811,9 @@
         <f t="shared" si="8"/>
         <v>201300</v>
       </c>
-      <c r="M223" s="11"/>
+      <c r="M223" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="224" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
@@ -9448,7 +9852,9 @@
         <f t="shared" si="8"/>
         <v>30900</v>
       </c>
-      <c r="M224" s="11"/>
+      <c r="M224" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="225" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
@@ -9487,7 +9893,9 @@
         <f t="shared" si="8"/>
         <v>70000</v>
       </c>
-      <c r="M225" s="11"/>
+      <c r="M225" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="226" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
@@ -9567,7 +9975,9 @@
         <f t="shared" si="8"/>
         <v>156600</v>
       </c>
-      <c r="M227" s="11"/>
+      <c r="M227" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="228" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
@@ -9647,7 +10057,9 @@
         <f t="shared" si="8"/>
         <v>14195</v>
       </c>
-      <c r="M229" s="11"/>
+      <c r="M229" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="230" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
@@ -9686,7 +10098,9 @@
         <f t="shared" si="8"/>
         <v>14195</v>
       </c>
-      <c r="M230" s="11"/>
+      <c r="M230" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="231" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
@@ -9753,7 +10167,9 @@
         <f t="shared" si="8"/>
         <v>6720</v>
       </c>
-      <c r="M232" s="11"/>
+      <c r="M232" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="233" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
@@ -9792,7 +10208,9 @@
         <f t="shared" si="8"/>
         <v>14195</v>
       </c>
-      <c r="M233" s="11"/>
+      <c r="M233" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="234" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
@@ -9831,7 +10249,9 @@
         <f t="shared" si="8"/>
         <v>14195</v>
       </c>
-      <c r="M234" s="11"/>
+      <c r="M234" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="235" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
@@ -9870,7 +10290,9 @@
         <f t="shared" si="8"/>
         <v>8150</v>
       </c>
-      <c r="M235" s="11"/>
+      <c r="M235" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="236" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
@@ -9909,7 +10331,9 @@
         <f t="shared" si="8"/>
         <v>8309</v>
       </c>
-      <c r="M236" s="11"/>
+      <c r="M236" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="237" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
@@ -9948,7 +10372,9 @@
         <f t="shared" si="8"/>
         <v>72000</v>
       </c>
-      <c r="M237" s="11"/>
+      <c r="M237" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="238" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
@@ -9989,7 +10415,9 @@
         <f t="shared" si="8"/>
         <v>5501</v>
       </c>
-      <c r="M238" s="11"/>
+      <c r="M238" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="239" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
@@ -10028,7 +10456,9 @@
         <f t="shared" si="8"/>
         <v>7000</v>
       </c>
-      <c r="M239" s="11"/>
+      <c r="M239" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="240" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
@@ -10067,7 +10497,9 @@
         <f t="shared" si="8"/>
         <v>4000</v>
       </c>
-      <c r="M240" s="11"/>
+      <c r="M240" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="241" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
@@ -10108,7 +10540,9 @@
         <f t="shared" si="8"/>
         <v>11844</v>
       </c>
-      <c r="M241" s="11"/>
+      <c r="M241" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="242" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
@@ -10147,7 +10581,9 @@
         <f t="shared" si="8"/>
         <v>15000</v>
       </c>
-      <c r="M242" s="10"/>
+      <c r="M242" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="243" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
@@ -10186,7 +10622,9 @@
         <f t="shared" si="8"/>
         <v>40000</v>
       </c>
-      <c r="M243" s="11"/>
+      <c r="M243" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="244" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
@@ -10225,7 +10663,9 @@
         <f t="shared" si="8"/>
         <v>30000</v>
       </c>
-      <c r="M244" s="11"/>
+      <c r="M244" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="245" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
@@ -10262,7 +10702,9 @@
         <f t="shared" si="8"/>
         <v>20000</v>
       </c>
-      <c r="M245" s="11"/>
+      <c r="M245" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="246" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
@@ -10303,7 +10745,9 @@
         <f t="shared" si="8"/>
         <v>2169</v>
       </c>
-      <c r="M246" s="11"/>
+      <c r="M246" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="247" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
@@ -10342,7 +10786,9 @@
         <f t="shared" si="8"/>
         <v>21800</v>
       </c>
-      <c r="M247" s="11"/>
+      <c r="M247" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="248" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
@@ -10381,7 +10827,9 @@
         <f t="shared" si="8"/>
         <v>30000</v>
       </c>
-      <c r="M248" s="11"/>
+      <c r="M248" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="249" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
@@ -10420,7 +10868,9 @@
         <f t="shared" si="8"/>
         <v>98000</v>
       </c>
-      <c r="M249" s="11"/>
+      <c r="M249" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="250" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
@@ -10459,7 +10909,9 @@
         <f t="shared" si="8"/>
         <v>57000</v>
       </c>
-      <c r="M250" s="11"/>
+      <c r="M250" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="251" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
@@ -10500,7 +10952,9 @@
         <f t="shared" si="8"/>
         <v>20068</v>
       </c>
-      <c r="M251" s="11"/>
+      <c r="M251" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="252" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
@@ -10541,7 +10995,9 @@
         <f t="shared" si="8"/>
         <v>15904</v>
       </c>
-      <c r="M252" s="11"/>
+      <c r="M252" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="253" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
@@ -10582,7 +11038,9 @@
         <f t="shared" si="8"/>
         <v>13320</v>
       </c>
-      <c r="M253" s="11"/>
+      <c r="M253" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="254" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
@@ -10623,7 +11081,9 @@
         <f t="shared" si="8"/>
         <v>13944</v>
       </c>
-      <c r="M254" s="11"/>
+      <c r="M254" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="255" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
@@ -10664,7 +11124,9 @@
         <f t="shared" si="8"/>
         <v>11166</v>
       </c>
-      <c r="M255" s="11"/>
+      <c r="M255" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="256" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
@@ -10703,7 +11165,9 @@
         <f t="shared" si="8"/>
         <v>22936</v>
       </c>
-      <c r="M256" s="11"/>
+      <c r="M256" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="257" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
@@ -10742,7 +11206,9 @@
         <f t="shared" si="8"/>
         <v>30820</v>
       </c>
-      <c r="M257" s="11"/>
+      <c r="M257" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="258" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
@@ -10781,7 +11247,9 @@
         <f t="shared" si="8"/>
         <v>15840</v>
       </c>
-      <c r="M258" s="11"/>
+      <c r="M258" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="259" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
@@ -10820,7 +11288,9 @@
         <f t="shared" si="8"/>
         <v>7440</v>
       </c>
-      <c r="M259" s="11"/>
+      <c r="M259" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="260" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
@@ -10859,7 +11329,9 @@
         <f t="shared" si="8"/>
         <v>3000</v>
       </c>
-      <c r="M260" s="11"/>
+      <c r="M260" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="261" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
@@ -10898,7 +11370,9 @@
         <f t="shared" si="8"/>
         <v>24000</v>
       </c>
-      <c r="M261" s="11"/>
+      <c r="M261" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="262" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
@@ -10937,7 +11411,9 @@
         <f t="shared" si="8"/>
         <v>12000</v>
       </c>
-      <c r="M262" s="11"/>
+      <c r="M262" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="263" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
@@ -10976,7 +11452,9 @@
         <f t="shared" ref="L263:L326" si="10">+J263-K263</f>
         <v>30000</v>
       </c>
-      <c r="M263" s="11"/>
+      <c r="M263" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="264" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
@@ -11015,7 +11493,9 @@
         <f t="shared" si="10"/>
         <v>7880</v>
       </c>
-      <c r="M264" s="11"/>
+      <c r="M264" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="265" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
@@ -11054,7 +11534,9 @@
         <f t="shared" si="10"/>
         <v>90000</v>
       </c>
-      <c r="M265" s="11"/>
+      <c r="M265" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="266" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
@@ -11093,7 +11575,9 @@
         <f t="shared" si="10"/>
         <v>12600</v>
       </c>
-      <c r="M266" s="11"/>
+      <c r="M266" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="267" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
@@ -11132,7 +11616,9 @@
         <f t="shared" si="10"/>
         <v>140000</v>
       </c>
-      <c r="M267" s="11"/>
+      <c r="M267" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="268" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
@@ -11171,7 +11657,9 @@
         <f t="shared" si="10"/>
         <v>19700</v>
       </c>
-      <c r="M268" s="11"/>
+      <c r="M268" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="269" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
@@ -11210,7 +11698,9 @@
         <f t="shared" si="10"/>
         <v>2000</v>
       </c>
-      <c r="M269" s="11"/>
+      <c r="M269" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="270" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
@@ -11249,7 +11739,9 @@
         <f t="shared" si="10"/>
         <v>26570</v>
       </c>
-      <c r="M270" s="11"/>
+      <c r="M270" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="271" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
@@ -11288,7 +11780,9 @@
         <f t="shared" si="10"/>
         <v>29000</v>
       </c>
-      <c r="M271" s="11"/>
+      <c r="M271" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="272" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
@@ -11368,7 +11862,9 @@
         <f t="shared" si="10"/>
         <v>2640</v>
       </c>
-      <c r="M273" s="11"/>
+      <c r="M273" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="274" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
@@ -11407,7 +11903,9 @@
         <f t="shared" si="10"/>
         <v>35000</v>
       </c>
-      <c r="M274" s="11"/>
+      <c r="M274" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="275" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
@@ -11446,7 +11944,9 @@
         <f t="shared" si="10"/>
         <v>20999</v>
       </c>
-      <c r="M275" s="11"/>
+      <c r="M275" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="276" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
@@ -11485,7 +11985,9 @@
         <f t="shared" si="10"/>
         <v>14000</v>
       </c>
-      <c r="M276" s="11"/>
+      <c r="M276" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="277" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
@@ -11524,7 +12026,9 @@
         <f t="shared" si="10"/>
         <v>275000</v>
       </c>
-      <c r="M277" s="11"/>
+      <c r="M277" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="278" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
@@ -11563,7 +12067,9 @@
         <f t="shared" si="10"/>
         <v>300000</v>
       </c>
-      <c r="M278" s="11"/>
+      <c r="M278" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="279" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
@@ -11602,7 +12108,9 @@
         <f t="shared" si="10"/>
         <v>20700</v>
       </c>
-      <c r="M279" s="11"/>
+      <c r="M279" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="280" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
@@ -11641,7 +12149,9 @@
         <f t="shared" si="10"/>
         <v>14400</v>
       </c>
-      <c r="M280" s="11"/>
+      <c r="M280" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="281" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
@@ -11721,7 +12231,9 @@
         <f t="shared" si="10"/>
         <v>5900</v>
       </c>
-      <c r="M282" s="11"/>
+      <c r="M282" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="283" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
@@ -11760,7 +12272,9 @@
         <f t="shared" si="10"/>
         <v>6937</v>
       </c>
-      <c r="M283" s="11"/>
+      <c r="M283" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="284" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
@@ -11840,7 +12354,9 @@
         <f t="shared" si="10"/>
         <v>70000</v>
       </c>
-      <c r="M285" s="11"/>
+      <c r="M285" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="286" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
@@ -11879,7 +12395,9 @@
         <f t="shared" si="10"/>
         <v>880000</v>
       </c>
-      <c r="M286" s="11"/>
+      <c r="M286" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="287" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
@@ -11918,7 +12436,9 @@
         <f t="shared" si="10"/>
         <v>52000</v>
       </c>
-      <c r="M287" s="11"/>
+      <c r="M287" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="288" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
@@ -11957,7 +12477,9 @@
         <f t="shared" si="10"/>
         <v>30000</v>
       </c>
-      <c r="M288" s="11"/>
+      <c r="M288" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="289" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
@@ -11996,7 +12518,9 @@
         <f t="shared" si="10"/>
         <v>12000</v>
       </c>
-      <c r="M289" s="11"/>
+      <c r="M289" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="290" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
@@ -12035,7 +12559,9 @@
         <f t="shared" si="10"/>
         <v>600000</v>
       </c>
-      <c r="M290" s="11"/>
+      <c r="M290" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="291" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
@@ -12074,7 +12600,9 @@
         <f t="shared" si="10"/>
         <v>300000</v>
       </c>
-      <c r="M291" s="11"/>
+      <c r="M291" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="292" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
@@ -12113,7 +12641,9 @@
         <f t="shared" si="10"/>
         <v>15500</v>
       </c>
-      <c r="M292" s="11"/>
+      <c r="M292" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="293" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
@@ -12152,7 +12682,9 @@
         <f t="shared" si="10"/>
         <v>46218</v>
       </c>
-      <c r="M293" s="11"/>
+      <c r="M293" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="294" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
@@ -12191,7 +12723,9 @@
         <f t="shared" si="10"/>
         <v>120000</v>
       </c>
-      <c r="M294" s="11"/>
+      <c r="M294" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="295" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
@@ -12271,7 +12805,9 @@
         <f t="shared" si="10"/>
         <v>17000</v>
       </c>
-      <c r="M296" s="11"/>
+      <c r="M296" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="297" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
@@ -12308,7 +12844,9 @@
         <f t="shared" si="10"/>
         <v>15000</v>
       </c>
-      <c r="M297" s="11"/>
+      <c r="M297" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="298" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
@@ -12347,7 +12885,9 @@
         <f t="shared" si="10"/>
         <v>30000</v>
       </c>
-      <c r="M298" s="11"/>
+      <c r="M298" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="299" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
@@ -12386,7 +12926,9 @@
         <f t="shared" si="10"/>
         <v>20000</v>
       </c>
-      <c r="M299" s="11"/>
+      <c r="M299" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="300" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A300" s="4" t="s">
@@ -12425,7 +12967,9 @@
         <f t="shared" si="10"/>
         <v>79992</v>
       </c>
-      <c r="M300" s="11"/>
+      <c r="M300" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="301" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
@@ -12464,7 +13008,9 @@
         <f t="shared" si="10"/>
         <v>9000</v>
       </c>
-      <c r="M301" s="11"/>
+      <c r="M301" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="302" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
@@ -12503,7 +13049,9 @@
         <f t="shared" si="10"/>
         <v>40880</v>
       </c>
-      <c r="M302" s="11"/>
+      <c r="M302" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="303" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
@@ -12542,7 +13090,9 @@
         <f t="shared" si="10"/>
         <v>4700</v>
       </c>
-      <c r="M303" s="11"/>
+      <c r="M303" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="304" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
@@ -12581,7 +13131,9 @@
         <f t="shared" si="10"/>
         <v>10600</v>
       </c>
-      <c r="M304" s="11"/>
+      <c r="M304" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="305" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
@@ -12620,7 +13172,9 @@
         <f t="shared" si="10"/>
         <v>17840</v>
       </c>
-      <c r="M305" s="11"/>
+      <c r="M305" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="306" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
@@ -12659,7 +13213,9 @@
         <f t="shared" si="10"/>
         <v>20080</v>
       </c>
-      <c r="M306" s="11"/>
+      <c r="M306" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="307" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
@@ -12698,7 +13254,9 @@
         <f t="shared" si="10"/>
         <v>7000</v>
       </c>
-      <c r="M307" s="11"/>
+      <c r="M307" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="308" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
@@ -12737,7 +13295,9 @@
         <f t="shared" si="10"/>
         <v>22833</v>
       </c>
-      <c r="M308" s="11"/>
+      <c r="M308" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="309" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
@@ -12776,7 +13336,9 @@
         <f t="shared" si="10"/>
         <v>20833</v>
       </c>
-      <c r="M309" s="11"/>
+      <c r="M309" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="310" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
@@ -12815,7 +13377,9 @@
         <f t="shared" si="10"/>
         <v>45000</v>
       </c>
-      <c r="M310" s="11"/>
+      <c r="M310" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="311" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
@@ -12854,7 +13418,9 @@
         <f t="shared" si="10"/>
         <v>77000</v>
       </c>
-      <c r="M311" s="11"/>
+      <c r="M311" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="312" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
@@ -12893,7 +13459,9 @@
         <f t="shared" si="10"/>
         <v>5700</v>
       </c>
-      <c r="M312" s="11"/>
+      <c r="M312" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="313" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
@@ -12932,7 +13500,9 @@
         <f t="shared" si="10"/>
         <v>12000</v>
       </c>
-      <c r="M313" s="11"/>
+      <c r="M313" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="314" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
@@ -12971,7 +13541,9 @@
         <f t="shared" si="10"/>
         <v>137200</v>
       </c>
-      <c r="M314" s="11"/>
+      <c r="M314" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="315" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
@@ -13010,7 +13582,9 @@
         <f t="shared" si="10"/>
         <v>174992</v>
       </c>
-      <c r="M315" s="11"/>
+      <c r="M315" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="316" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
@@ -13049,7 +13623,9 @@
         <f t="shared" si="10"/>
         <v>268105</v>
       </c>
-      <c r="M316" s="11"/>
+      <c r="M316" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="317" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
@@ -13088,7 +13664,9 @@
         <f t="shared" si="10"/>
         <v>49448</v>
       </c>
-      <c r="M317" s="11"/>
+      <c r="M317" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="318" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
@@ -13127,7 +13705,9 @@
         <f t="shared" si="10"/>
         <v>515251</v>
       </c>
-      <c r="M318" s="11"/>
+      <c r="M318" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="319" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
@@ -13166,7 +13746,9 @@
         <f t="shared" si="10"/>
         <v>394661</v>
       </c>
-      <c r="M319" s="11"/>
+      <c r="M319" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="320" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
@@ -13205,7 +13787,9 @@
         <f t="shared" si="10"/>
         <v>55518</v>
       </c>
-      <c r="M320" s="11"/>
+      <c r="M320" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="321" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
@@ -13244,7 +13828,9 @@
         <f t="shared" si="10"/>
         <v>66138</v>
       </c>
-      <c r="M321" s="11"/>
+      <c r="M321" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="322" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
@@ -13283,7 +13869,9 @@
         <f t="shared" si="10"/>
         <v>22952</v>
       </c>
-      <c r="M322" s="11"/>
+      <c r="M322" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="323" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
@@ -13322,7 +13910,9 @@
         <f t="shared" si="10"/>
         <v>300000</v>
       </c>
-      <c r="M323" s="11"/>
+      <c r="M323" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="324" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A324" s="4" t="s">
@@ -13359,7 +13949,9 @@
         <f t="shared" si="10"/>
         <v>12000</v>
       </c>
-      <c r="M324" s="11"/>
+      <c r="M324" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="325" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
@@ -13398,7 +13990,9 @@
         <f t="shared" si="10"/>
         <v>49000</v>
       </c>
-      <c r="M325" s="11"/>
+      <c r="M325" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="326" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
@@ -13478,7 +14072,9 @@
         <f t="shared" ref="L327:L391" si="12">+J327-K327</f>
         <v>165400</v>
       </c>
-      <c r="M327" s="11"/>
+      <c r="M327" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="328" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
@@ -13517,7 +14113,9 @@
         <f t="shared" si="12"/>
         <v>203775</v>
       </c>
-      <c r="M328" s="11"/>
+      <c r="M328" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="329" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
@@ -13556,7 +14154,9 @@
         <f t="shared" si="12"/>
         <v>472000</v>
       </c>
-      <c r="M329" s="11"/>
+      <c r="M329" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="330" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
@@ -13636,7 +14236,9 @@
         <f t="shared" si="12"/>
         <v>42925</v>
       </c>
-      <c r="M331" s="11"/>
+      <c r="M331" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="332" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
@@ -13716,7 +14318,9 @@
         <f t="shared" si="12"/>
         <v>16160</v>
       </c>
-      <c r="M333" s="11"/>
+      <c r="M333" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="334" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A334" s="4" t="s">
@@ -13755,7 +14359,9 @@
         <f t="shared" si="12"/>
         <v>16160</v>
       </c>
-      <c r="M334" s="11"/>
+      <c r="M334" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="335" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
@@ -13819,7 +14425,9 @@
         <f t="shared" si="12"/>
         <v>16160</v>
       </c>
-      <c r="M336" s="11"/>
+      <c r="M336" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="337" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
@@ -13858,7 +14466,9 @@
         <f t="shared" si="12"/>
         <v>16160</v>
       </c>
-      <c r="M337" s="11"/>
+      <c r="M337" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="338" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
@@ -13897,7 +14507,9 @@
         <f t="shared" si="12"/>
         <v>75200</v>
       </c>
-      <c r="M338" s="11"/>
+      <c r="M338" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="339" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A339" s="4" t="s">
@@ -13936,7 +14548,9 @@
         <f t="shared" si="12"/>
         <v>133152</v>
       </c>
-      <c r="M339" s="11"/>
+      <c r="M339" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="340" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A340" s="4" t="s">
@@ -13975,7 +14589,9 @@
         <f t="shared" si="12"/>
         <v>8625</v>
       </c>
-      <c r="M340" s="11"/>
+      <c r="M340" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="341" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
@@ -14014,7 +14630,9 @@
         <f t="shared" si="12"/>
         <v>703000</v>
       </c>
-      <c r="M341" s="11"/>
+      <c r="M341" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="342" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
@@ -14053,7 +14671,9 @@
         <f t="shared" si="12"/>
         <v>6937</v>
       </c>
-      <c r="M342" s="11"/>
+      <c r="M342" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="343" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
@@ -14092,7 +14712,9 @@
         <f t="shared" si="12"/>
         <v>45760</v>
       </c>
-      <c r="M343" s="11"/>
+      <c r="M343" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="344" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A344" s="4" t="s">
@@ -14131,7 +14753,9 @@
         <f t="shared" si="12"/>
         <v>48400</v>
       </c>
-      <c r="M344" s="11"/>
+      <c r="M344" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="345" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
@@ -14168,7 +14792,9 @@
         <f t="shared" si="12"/>
         <v>119800</v>
       </c>
-      <c r="M345" s="10"/>
+      <c r="M345" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="346" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
@@ -14207,7 +14833,9 @@
         <f t="shared" si="12"/>
         <v>34000</v>
       </c>
-      <c r="M346" s="11"/>
+      <c r="M346" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="347" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
@@ -14246,7 +14874,9 @@
         <f t="shared" si="12"/>
         <v>12859</v>
       </c>
-      <c r="M347" s="11"/>
+      <c r="M347" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="348" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
@@ -14285,7 +14915,9 @@
         <f t="shared" si="12"/>
         <v>33500</v>
       </c>
-      <c r="M348" s="11"/>
+      <c r="M348" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="349" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A349" s="4" t="s">
@@ -14324,7 +14956,9 @@
         <f t="shared" si="12"/>
         <v>35500</v>
       </c>
-      <c r="M349" s="11"/>
+      <c r="M349" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="350" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
@@ -14363,7 +14997,9 @@
         <f t="shared" si="12"/>
         <v>12000</v>
       </c>
-      <c r="M350" s="11"/>
+      <c r="M350" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="351" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A351" s="4" t="s">
@@ -14400,7 +15036,9 @@
         <f t="shared" si="12"/>
         <v>35200</v>
       </c>
-      <c r="M351" s="11"/>
+      <c r="M351" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="352" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
@@ -14437,7 +15075,9 @@
         <f t="shared" si="12"/>
         <v>130400</v>
       </c>
-      <c r="M352" s="11"/>
+      <c r="M352" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="353" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
@@ -14474,7 +15114,9 @@
         <f t="shared" si="12"/>
         <v>25000</v>
       </c>
-      <c r="M353" s="11"/>
+      <c r="M353" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="354" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A354" s="4" t="s">
@@ -14511,7 +15153,9 @@
         <f t="shared" si="12"/>
         <v>8784</v>
       </c>
-      <c r="M354" s="11"/>
+      <c r="M354" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="355" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A355" s="4" t="s">
@@ -14550,7 +15194,9 @@
         <f t="shared" si="12"/>
         <v>90000</v>
       </c>
-      <c r="M355" s="11"/>
+      <c r="M355" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="356" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
@@ -14589,7 +15235,9 @@
         <f t="shared" si="12"/>
         <v>4700</v>
       </c>
-      <c r="M356" s="11"/>
+      <c r="M356" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="357" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
@@ -14628,7 +15276,9 @@
         <f t="shared" si="12"/>
         <v>137200</v>
       </c>
-      <c r="M357" s="11"/>
+      <c r="M357" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="358" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
@@ -14667,7 +15317,9 @@
         <f t="shared" si="12"/>
         <v>7500</v>
       </c>
-      <c r="M358" s="11"/>
+      <c r="M358" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="359" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
@@ -14706,7 +15358,9 @@
         <f t="shared" si="12"/>
         <v>15000</v>
       </c>
-      <c r="M359" s="11"/>
+      <c r="M359" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="360" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
@@ -14743,7 +15397,9 @@
         <f t="shared" si="12"/>
         <v>20000</v>
       </c>
-      <c r="M360" s="11"/>
+      <c r="M360" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="361" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
@@ -14782,7 +15438,9 @@
         <f t="shared" si="12"/>
         <v>25000</v>
       </c>
-      <c r="M361" s="11"/>
+      <c r="M361" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="362" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A362" s="4" t="s">
@@ -14821,7 +15479,9 @@
         <f t="shared" si="12"/>
         <v>16000</v>
       </c>
-      <c r="M362" s="11"/>
+      <c r="M362" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="363" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A363" s="4" t="s">
@@ -14860,7 +15520,9 @@
         <f t="shared" si="12"/>
         <v>3750</v>
       </c>
-      <c r="M363" s="11"/>
+      <c r="M363" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="364" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
@@ -14899,7 +15561,9 @@
         <f t="shared" si="12"/>
         <v>9750</v>
       </c>
-      <c r="M364" s="11"/>
+      <c r="M364" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="365" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A365" s="4" t="s">
@@ -14938,7 +15602,9 @@
         <f t="shared" si="12"/>
         <v>14250</v>
       </c>
-      <c r="M365" s="11"/>
+      <c r="M365" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="366" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A366" s="4" t="s">
@@ -14977,7 +15643,9 @@
         <f t="shared" si="12"/>
         <v>12750</v>
       </c>
-      <c r="M366" s="11"/>
+      <c r="M366" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="367" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A367" s="4" t="s">
@@ -15016,7 +15684,9 @@
         <f t="shared" si="12"/>
         <v>7500</v>
       </c>
-      <c r="M367" s="11"/>
+      <c r="M367" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="368" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
@@ -15055,7 +15725,9 @@
         <f t="shared" si="12"/>
         <v>28500</v>
       </c>
-      <c r="M368" s="11"/>
+      <c r="M368" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="369" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A369" s="4" t="s">
@@ -15094,7 +15766,9 @@
         <f t="shared" si="12"/>
         <v>14250</v>
       </c>
-      <c r="M369" s="11"/>
+      <c r="M369" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="370" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A370" s="4" t="s">
@@ -15133,7 +15807,9 @@
         <f t="shared" si="12"/>
         <v>6000</v>
       </c>
-      <c r="M370" s="11"/>
+      <c r="M370" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="371" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
@@ -15213,7 +15889,9 @@
         <f t="shared" si="12"/>
         <v>2640</v>
       </c>
-      <c r="M372" s="11"/>
+      <c r="M372" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="373" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
@@ -15252,7 +15930,9 @@
         <f t="shared" si="12"/>
         <v>5040</v>
       </c>
-      <c r="M373" s="11"/>
+      <c r="M373" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="374" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A374" s="4" t="s">
@@ -15291,7 +15971,9 @@
         <f t="shared" si="12"/>
         <v>100000</v>
       </c>
-      <c r="M374" s="11"/>
+      <c r="M374" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="375" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A375" s="4" t="s">
@@ -15330,7 +16012,9 @@
         <f t="shared" si="12"/>
         <v>110000</v>
       </c>
-      <c r="M375" s="11"/>
+      <c r="M375" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="376" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
@@ -15369,7 +16053,9 @@
         <f t="shared" si="12"/>
         <v>178000</v>
       </c>
-      <c r="M376" s="11"/>
+      <c r="M376" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="377" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
@@ -15406,7 +16092,9 @@
         <f t="shared" si="12"/>
         <v>153000</v>
       </c>
-      <c r="M377" s="11"/>
+      <c r="M377" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="378" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
@@ -15445,7 +16133,9 @@
         <f t="shared" si="12"/>
         <v>154453</v>
       </c>
-      <c r="M378" s="11"/>
+      <c r="M378" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="379" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A379" s="4" t="s">
@@ -15525,7 +16215,9 @@
         <f t="shared" si="12"/>
         <v>5000</v>
       </c>
-      <c r="M380" s="11"/>
+      <c r="M380" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="381" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A381" s="4" t="s">
@@ -15564,7 +16256,9 @@
         <f t="shared" si="12"/>
         <v>3080</v>
       </c>
-      <c r="M381" s="11"/>
+      <c r="M381" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="382" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
@@ -15644,7 +16338,9 @@
         <f t="shared" si="12"/>
         <v>7000</v>
       </c>
-      <c r="M383" s="11"/>
+      <c r="M383" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="384" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A384" s="4" t="s">
@@ -15683,7 +16379,9 @@
         <f t="shared" si="12"/>
         <v>6937</v>
       </c>
-      <c r="M384" s="11"/>
+      <c r="M384" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="385" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A385" s="4" t="s">
@@ -15722,7 +16420,9 @@
         <f t="shared" si="12"/>
         <v>128700</v>
       </c>
-      <c r="M385" s="11"/>
+      <c r="M385" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="386" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A386" s="4" t="s">
@@ -15802,7 +16502,9 @@
         <f t="shared" si="12"/>
         <v>703000</v>
       </c>
-      <c r="M387" s="11"/>
+      <c r="M387" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="388" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
@@ -15841,7 +16543,9 @@
         <f t="shared" si="12"/>
         <v>29475</v>
       </c>
-      <c r="M388" s="11"/>
+      <c r="M388" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="389" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
@@ -15880,7 +16584,9 @@
         <f t="shared" si="12"/>
         <v>30000</v>
       </c>
-      <c r="M389" s="11"/>
+      <c r="M389" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="390" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A390" s="4" t="s">
@@ -15919,7 +16625,9 @@
         <f t="shared" si="12"/>
         <v>11014</v>
       </c>
-      <c r="M390" s="11"/>
+      <c r="M390" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="391" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A391" s="4" t="s">
@@ -15958,7 +16666,9 @@
         <f t="shared" si="12"/>
         <v>4000</v>
       </c>
-      <c r="M391" s="11"/>
+      <c r="M391" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="392" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A392" s="4" t="s">
@@ -15997,7 +16707,9 @@
         <f t="shared" ref="L392:L455" si="14">+J392-K392</f>
         <v>16000</v>
       </c>
-      <c r="M392" s="11"/>
+      <c r="M392" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="393" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
@@ -16036,7 +16748,9 @@
         <f t="shared" si="14"/>
         <v>46469</v>
       </c>
-      <c r="M393" s="11"/>
+      <c r="M393" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="394" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A394" s="4" t="s">
@@ -16073,7 +16787,9 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M394" s="11"/>
+      <c r="M394" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="395" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A395" s="4" t="s">
@@ -16110,7 +16826,9 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M395" s="11"/>
+      <c r="M395" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="396" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A396" s="4" t="s">
@@ -16147,7 +16865,9 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M396" s="11"/>
+      <c r="M396" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="397" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A397" s="4" t="s">
@@ -16184,7 +16904,9 @@
         <f t="shared" si="14"/>
         <v>90000</v>
       </c>
-      <c r="M397" s="11"/>
+      <c r="M397" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="398" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A398" s="4" t="s">
@@ -16221,7 +16943,9 @@
         <f t="shared" si="14"/>
         <v>7500</v>
       </c>
-      <c r="M398" s="11"/>
+      <c r="M398" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="399" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
@@ -16258,7 +16982,9 @@
         <f t="shared" si="14"/>
         <v>90400</v>
       </c>
-      <c r="M399" s="11"/>
+      <c r="M399" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="400" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
@@ -16295,7 +17021,9 @@
         <f t="shared" si="14"/>
         <v>50000</v>
       </c>
-      <c r="M400" s="11"/>
+      <c r="M400" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="401" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A401" s="4" t="s">
@@ -16332,7 +17060,9 @@
         <f t="shared" si="14"/>
         <v>36204</v>
       </c>
-      <c r="M401" s="11"/>
+      <c r="M401" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="402" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
@@ -16369,7 +17099,9 @@
         <f t="shared" si="14"/>
         <v>26301</v>
       </c>
-      <c r="M402" s="11"/>
+      <c r="M402" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="403" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A403" s="4" t="s">
@@ -16408,7 +17140,9 @@
         <f t="shared" si="14"/>
         <v>6750</v>
       </c>
-      <c r="M403" s="11"/>
+      <c r="M403" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="404" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
@@ -16447,7 +17181,9 @@
         <f t="shared" si="14"/>
         <v>14250</v>
       </c>
-      <c r="M404" s="11"/>
+      <c r="M404" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="405" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A405" s="4" t="s">
@@ -16484,7 +17220,9 @@
         <f t="shared" si="14"/>
         <v>14250</v>
       </c>
-      <c r="M405" s="11"/>
+      <c r="M405" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="406" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A406" s="4" t="s">
@@ -16564,7 +17302,9 @@
         <f t="shared" si="14"/>
         <v>94900</v>
       </c>
-      <c r="M407" s="11"/>
+      <c r="M407" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="408" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
@@ -16603,7 +17343,9 @@
         <f t="shared" si="14"/>
         <v>104000</v>
       </c>
-      <c r="M408" s="11"/>
+      <c r="M408" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="409" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A409" s="4" t="s">
@@ -16642,7 +17384,9 @@
         <f t="shared" si="14"/>
         <v>5040</v>
       </c>
-      <c r="M409" s="11"/>
+      <c r="M409" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="410" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A410" s="4" t="s">
@@ -16672,7 +17416,9 @@
       <c r="L410" s="8">
         <v>1086569</v>
       </c>
-      <c r="M410" s="11"/>
+      <c r="M410" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="411" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A411" s="4" t="s">
@@ -16793,7 +17539,9 @@
         <f t="shared" si="14"/>
         <v>52938</v>
       </c>
-      <c r="M413" s="11"/>
+      <c r="M413" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="414" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A414" s="4" t="s">
@@ -16832,7 +17580,9 @@
         <f t="shared" si="14"/>
         <v>461831</v>
       </c>
-      <c r="M414" s="11"/>
+      <c r="M414" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="415" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A415" s="4" t="s">
@@ -16871,7 +17621,9 @@
         <f t="shared" si="14"/>
         <v>132000</v>
       </c>
-      <c r="M415" s="11"/>
+      <c r="M415" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="416" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A416" s="4" t="s">
@@ -16910,7 +17662,9 @@
         <f t="shared" si="14"/>
         <v>6937</v>
       </c>
-      <c r="M416" s="11"/>
+      <c r="M416" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="417" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
@@ -16949,7 +17703,9 @@
         <f t="shared" si="14"/>
         <v>60000</v>
       </c>
-      <c r="M417" s="11"/>
+      <c r="M417" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="418" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A418" s="4" t="s">
@@ -17029,7 +17785,9 @@
         <f t="shared" si="14"/>
         <v>24000</v>
       </c>
-      <c r="M419" s="11"/>
+      <c r="M419" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="420" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A420" s="4" t="s">
@@ -17068,7 +17826,9 @@
         <f t="shared" si="14"/>
         <v>24000</v>
       </c>
-      <c r="M420" s="11"/>
+      <c r="M420" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="421" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A421" s="4" t="s">
@@ -17107,7 +17867,9 @@
         <f t="shared" si="14"/>
         <v>7000</v>
       </c>
-      <c r="M421" s="11"/>
+      <c r="M421" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="422" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A422" s="4" t="s">
@@ -17146,7 +17908,9 @@
         <f t="shared" si="14"/>
         <v>26250</v>
       </c>
-      <c r="M422" s="11"/>
+      <c r="M422" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="423" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A423" s="4" t="s">
@@ -17185,7 +17949,9 @@
         <f t="shared" si="14"/>
         <v>42000</v>
       </c>
-      <c r="M423" s="11"/>
+      <c r="M423" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="424" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A424" s="4" t="s">
@@ -17224,7 +17990,9 @@
         <f t="shared" si="14"/>
         <v>126926</v>
       </c>
-      <c r="M424" s="11"/>
+      <c r="M424" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="425" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
@@ -17263,7 +18031,9 @@
         <f t="shared" si="14"/>
         <v>3000</v>
       </c>
-      <c r="M425" s="11"/>
+      <c r="M425" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="426" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A426" s="4" t="s">
@@ -17302,7 +18072,9 @@
         <f t="shared" si="14"/>
         <v>12600</v>
       </c>
-      <c r="M426" s="11"/>
+      <c r="M426" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="427" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A427" s="4" t="s">
@@ -17341,7 +18113,9 @@
         <f t="shared" si="14"/>
         <v>128700</v>
       </c>
-      <c r="M427" s="11"/>
+      <c r="M427" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="428" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A428" s="4" t="s">
@@ -17380,7 +18154,9 @@
         <f t="shared" si="14"/>
         <v>25000</v>
       </c>
-      <c r="M428" s="11"/>
+      <c r="M428" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="429" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A429" s="4" t="s">
@@ -17419,7 +18195,9 @@
         <f t="shared" si="14"/>
         <v>450000</v>
       </c>
-      <c r="M429" s="11"/>
+      <c r="M429" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="430" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A430" s="4" t="s">
@@ -17458,7 +18236,9 @@
         <f t="shared" si="14"/>
         <v>120000</v>
       </c>
-      <c r="M430" s="11"/>
+      <c r="M430" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="431" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A431" s="4" t="s">
@@ -17497,7 +18277,9 @@
         <f t="shared" si="14"/>
         <v>300000</v>
       </c>
-      <c r="M431" s="11"/>
+      <c r="M431" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="432" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
@@ -17536,7 +18318,9 @@
         <f t="shared" si="14"/>
         <v>113700</v>
       </c>
-      <c r="M432" s="11"/>
+      <c r="M432" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="433" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
@@ -17573,7 +18357,9 @@
         <f t="shared" si="14"/>
         <v>83000</v>
       </c>
-      <c r="M433" s="11"/>
+      <c r="M433" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="434" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A434" s="4" t="s">
@@ -17610,7 +18396,9 @@
         <f t="shared" si="14"/>
         <v>15000</v>
       </c>
-      <c r="M434" s="11"/>
+      <c r="M434" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="435" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A435" s="4" t="s">
@@ -17647,7 +18435,9 @@
         <f t="shared" si="14"/>
         <v>39646</v>
       </c>
-      <c r="M435" s="11"/>
+      <c r="M435" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="436" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A436" s="4" t="s">
@@ -17684,7 +18474,9 @@
         <f t="shared" si="14"/>
         <v>18242</v>
       </c>
-      <c r="M436" s="11"/>
+      <c r="M436" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="437" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A437" s="4" t="s">
@@ -17721,7 +18513,9 @@
         <f t="shared" si="14"/>
         <v>110572</v>
       </c>
-      <c r="M437" s="11"/>
+      <c r="M437" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="438" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A438" s="4" t="s">
@@ -17758,7 +18552,9 @@
         <f t="shared" si="14"/>
         <v>83006</v>
       </c>
-      <c r="M438" s="11"/>
+      <c r="M438" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="439" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A439" s="4" t="s">
@@ -17795,7 +18591,9 @@
         <f t="shared" si="14"/>
         <v>49825</v>
       </c>
-      <c r="M439" s="11"/>
+      <c r="M439" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="440" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A440" s="4" t="s">
@@ -17832,7 +18630,9 @@
         <f t="shared" si="14"/>
         <v>72000</v>
       </c>
-      <c r="M440" s="11"/>
+      <c r="M440" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="441" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A441" s="4" t="s">
@@ -17869,7 +18669,9 @@
         <f t="shared" si="14"/>
         <v>78000</v>
       </c>
-      <c r="M441" s="11"/>
+      <c r="M441" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="442" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A442" s="4" t="s">
@@ -17906,7 +18708,9 @@
         <f t="shared" si="14"/>
         <v>29475</v>
       </c>
-      <c r="M442" s="11"/>
+      <c r="M442" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="443" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A443" s="4" t="s">
@@ -17986,7 +18790,9 @@
         <f t="shared" si="14"/>
         <v>97233</v>
       </c>
-      <c r="M444" s="11"/>
+      <c r="M444" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="445" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
@@ -18025,7 +18831,9 @@
         <f t="shared" si="14"/>
         <v>30000</v>
       </c>
-      <c r="M445" s="11"/>
+      <c r="M445" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="446" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A446" s="4" t="s">
@@ -18064,7 +18872,9 @@
         <f t="shared" si="14"/>
         <v>108000</v>
       </c>
-      <c r="M446" s="11"/>
+      <c r="M446" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="447" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A447" s="4" t="s">
@@ -18101,7 +18911,9 @@
         <f t="shared" si="14"/>
         <v>60000</v>
       </c>
-      <c r="M447" s="11"/>
+      <c r="M447" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="448" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A448" s="4" t="s">
@@ -18140,7 +18952,9 @@
         <f t="shared" si="14"/>
         <v>10000</v>
       </c>
-      <c r="M448" s="11"/>
+      <c r="M448" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="449" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A449" s="4" t="s">
@@ -18170,7 +18984,9 @@
       <c r="L449" s="8">
         <v>183456</v>
       </c>
-      <c r="M449" s="11"/>
+      <c r="M449" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="450" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
@@ -18250,7 +19066,9 @@
         <f t="shared" si="14"/>
         <v>100000</v>
       </c>
-      <c r="M451" s="11"/>
+      <c r="M451" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="452" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
@@ -18289,7 +19107,9 @@
         <f t="shared" si="14"/>
         <v>150000</v>
       </c>
-      <c r="M452" s="11"/>
+      <c r="M452" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="453" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A453" s="4" t="s">
@@ -18328,7 +19148,9 @@
         <f t="shared" si="14"/>
         <v>144000</v>
       </c>
-      <c r="M453" s="11"/>
+      <c r="M453" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="454" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A454" s="4" t="s">
@@ -18367,7 +19189,9 @@
         <f t="shared" si="14"/>
         <v>20000</v>
       </c>
-      <c r="M454" s="11"/>
+      <c r="M454" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="455" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A455" s="4" t="s">
@@ -18406,7 +19230,9 @@
         <f t="shared" si="14"/>
         <v>20000</v>
       </c>
-      <c r="M455" s="11"/>
+      <c r="M455" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="456" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A456" s="4" t="s">
@@ -18445,7 +19271,9 @@
         <f t="shared" ref="L456:L495" si="17">+J456-K456</f>
         <v>61500</v>
       </c>
-      <c r="M456" s="11"/>
+      <c r="M456" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="457" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A457" s="4" t="s">
@@ -18525,7 +19353,9 @@
         <f t="shared" si="17"/>
         <v>3200</v>
       </c>
-      <c r="M458" s="11"/>
+      <c r="M458" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="459" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A459" s="4" t="s">
@@ -18564,7 +19394,9 @@
         <f t="shared" si="17"/>
         <v>12000</v>
       </c>
-      <c r="M459" s="11"/>
+      <c r="M459" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="460" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A460" s="4" t="s">
@@ -18603,7 +19435,9 @@
         <f t="shared" si="17"/>
         <v>7000</v>
       </c>
-      <c r="M460" s="11"/>
+      <c r="M460" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="461" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A461" s="4" t="s">
@@ -18683,7 +19517,9 @@
         <f t="shared" si="17"/>
         <v>602944</v>
       </c>
-      <c r="M462" s="11"/>
+      <c r="M462" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="463" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A463" s="4" t="s">
@@ -18722,7 +19558,9 @@
         <f t="shared" si="17"/>
         <v>34900</v>
       </c>
-      <c r="M463" s="11"/>
+      <c r="M463" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="464" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A464" s="4" t="s">
@@ -18761,7 +19599,9 @@
         <f t="shared" si="17"/>
         <v>17000</v>
       </c>
-      <c r="M464" s="11"/>
+      <c r="M464" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="465" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
@@ -18800,7 +19640,9 @@
         <f t="shared" si="17"/>
         <v>25000</v>
       </c>
-      <c r="M465" s="11"/>
+      <c r="M465" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="466" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A466" s="4" t="s">
@@ -18839,7 +19681,9 @@
         <f t="shared" si="17"/>
         <v>1056948</v>
       </c>
-      <c r="M466" s="11"/>
+      <c r="M466" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="467" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A467" s="4" t="s">
@@ -18878,7 +19722,9 @@
         <f t="shared" si="17"/>
         <v>20000</v>
       </c>
-      <c r="M467" s="11"/>
+      <c r="M467" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="468" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A468" s="4" t="s">
@@ -18917,7 +19763,9 @@
         <f t="shared" si="17"/>
         <v>7200</v>
       </c>
-      <c r="M468" s="11"/>
+      <c r="M468" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="469" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A469" s="4" t="s">
@@ -18956,7 +19804,9 @@
         <f t="shared" si="17"/>
         <v>90000</v>
       </c>
-      <c r="M469" s="11"/>
+      <c r="M469" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="470" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A470" s="4" t="s">
@@ -18995,7 +19845,9 @@
         <f t="shared" si="17"/>
         <v>7500</v>
       </c>
-      <c r="M470" s="11"/>
+      <c r="M470" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="471" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A471" s="4" t="s">
@@ -19034,7 +19886,9 @@
         <f t="shared" si="17"/>
         <v>3000</v>
       </c>
-      <c r="M471" s="11"/>
+      <c r="M471" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="472" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A472" s="4" t="s">
@@ -19073,7 +19927,9 @@
         <f t="shared" si="17"/>
         <v>12560</v>
       </c>
-      <c r="M472" s="11"/>
+      <c r="M472" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="473" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A473" s="4" t="s">
@@ -19112,7 +19968,9 @@
         <f t="shared" si="17"/>
         <v>17600</v>
       </c>
-      <c r="M473" s="11"/>
+      <c r="M473" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="474" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A474" s="4" t="s">
@@ -19151,7 +20009,9 @@
         <f t="shared" si="17"/>
         <v>5170</v>
       </c>
-      <c r="M474" s="11"/>
+      <c r="M474" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="475" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A475" s="4" t="s">
@@ -19190,7 +20050,9 @@
         <f t="shared" si="17"/>
         <v>52938</v>
       </c>
-      <c r="M475" s="11"/>
+      <c r="M475" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="476" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A476" s="4" t="s">
@@ -19229,7 +20091,9 @@
         <f t="shared" si="17"/>
         <v>52938</v>
       </c>
-      <c r="M476" s="11"/>
+      <c r="M476" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="477" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A477" s="4" t="s">
@@ -19268,7 +20132,9 @@
         <f t="shared" si="17"/>
         <v>7880</v>
       </c>
-      <c r="M477" s="11"/>
+      <c r="M477" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="478" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A478" s="4" t="s">
@@ -19307,7 +20173,9 @@
         <f t="shared" si="17"/>
         <v>10200</v>
       </c>
-      <c r="M478" s="11"/>
+      <c r="M478" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="479" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A479" s="4" t="s">
@@ -19346,7 +20214,9 @@
         <f t="shared" si="17"/>
         <v>2500</v>
       </c>
-      <c r="M479" s="11"/>
+      <c r="M479" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="480" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A480" s="4" t="s">
@@ -19385,7 +20255,9 @@
         <f t="shared" si="17"/>
         <v>3600</v>
       </c>
-      <c r="M480" s="11"/>
+      <c r="M480" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="481" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
@@ -19424,7 +20296,9 @@
         <f t="shared" si="17"/>
         <v>10833</v>
       </c>
-      <c r="M481" s="11"/>
+      <c r="M481" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="482" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A482" s="4" t="s">
@@ -19463,7 +20337,9 @@
         <f t="shared" si="17"/>
         <v>10833</v>
       </c>
-      <c r="M482" s="11"/>
+      <c r="M482" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="483" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A483" s="4" t="s">
@@ -19502,7 +20378,9 @@
         <f t="shared" si="17"/>
         <v>10833</v>
       </c>
-      <c r="M483" s="11"/>
+      <c r="M483" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="484" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A484" s="4" t="s">
@@ -19541,7 +20419,9 @@
         <f t="shared" si="17"/>
         <v>10300</v>
       </c>
-      <c r="M484" s="11"/>
+      <c r="M484" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="485" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A485" s="4" t="s">
@@ -19580,7 +20460,9 @@
         <f t="shared" si="17"/>
         <v>10300</v>
       </c>
-      <c r="M485" s="11"/>
+      <c r="M485" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="486" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A486" s="4" t="s">
@@ -19619,7 +20501,9 @@
         <f t="shared" si="17"/>
         <v>10300</v>
       </c>
-      <c r="M486" s="11"/>
+      <c r="M486" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="487" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A487" s="4" t="s">
@@ -19658,7 +20542,9 @@
         <f t="shared" si="17"/>
         <v>10300</v>
       </c>
-      <c r="M487" s="11"/>
+      <c r="M487" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="488" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A488" s="4" t="s">
@@ -19697,7 +20583,9 @@
         <f t="shared" si="17"/>
         <v>10300</v>
       </c>
-      <c r="M488" s="11"/>
+      <c r="M488" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="489" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A489" s="4" t="s">
@@ -19736,7 +20624,9 @@
         <f t="shared" si="17"/>
         <v>10300</v>
       </c>
-      <c r="M489" s="11"/>
+      <c r="M489" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="490" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A490" s="4" t="s">
@@ -19775,7 +20665,9 @@
         <f t="shared" si="17"/>
         <v>10300</v>
       </c>
-      <c r="M490" s="11"/>
+      <c r="M490" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="491" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A491" s="4" t="s">
@@ -19855,7 +20747,9 @@
         <f t="shared" si="17"/>
         <v>30000</v>
       </c>
-      <c r="M492" s="11"/>
+      <c r="M492" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="493" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
@@ -19894,7 +20788,9 @@
         <f t="shared" si="17"/>
         <v>144000</v>
       </c>
-      <c r="M493" s="11"/>
+      <c r="M493" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="494" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A494" s="4" t="s">
@@ -19933,7 +20829,9 @@
         <f t="shared" si="17"/>
         <v>86200</v>
       </c>
-      <c r="M494" s="11"/>
+      <c r="M494" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="495" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A495" s="4" t="s">
@@ -19972,7 +20870,9 @@
         <f t="shared" si="17"/>
         <v>81000</v>
       </c>
-      <c r="M495" s="11"/>
+      <c r="M495" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="496" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A496" s="4" t="s">
@@ -20002,7 +20902,9 @@
       <c r="L496" s="8">
         <v>493452</v>
       </c>
-      <c r="M496" s="11"/>
+      <c r="M496" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="497" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A497" s="4" t="s">
@@ -20123,7 +21025,9 @@
         <f t="shared" si="18"/>
         <v>6937</v>
       </c>
-      <c r="M499" s="11"/>
+      <c r="M499" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="500" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A500" s="4" t="s">
@@ -20162,7 +21066,9 @@
         <f t="shared" si="18"/>
         <v>2733</v>
       </c>
-      <c r="M500" s="11"/>
+      <c r="M500" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="501" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A501" s="4" t="s">
@@ -20201,7 +21107,9 @@
         <f t="shared" si="18"/>
         <v>12000</v>
       </c>
-      <c r="M501" s="11"/>
+      <c r="M501" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="502" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A502" s="4" t="s">
@@ -20240,7 +21148,9 @@
         <f t="shared" si="18"/>
         <v>3000</v>
       </c>
-      <c r="M502" s="11"/>
+      <c r="M502" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="503" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A503" s="4" t="s">
@@ -20279,7 +21189,9 @@
         <f t="shared" si="18"/>
         <v>58200</v>
       </c>
-      <c r="M503" s="11"/>
+      <c r="M503" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="504" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A504" s="4" t="s">
@@ -20318,7 +21230,9 @@
         <f t="shared" si="18"/>
         <v>11500</v>
       </c>
-      <c r="M504" s="11"/>
+      <c r="M504" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="505" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A505" s="4" t="s">
@@ -20357,7 +21271,9 @@
         <f t="shared" si="18"/>
         <v>12314</v>
       </c>
-      <c r="M505" s="11"/>
+      <c r="M505" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="506" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A506" s="4" t="s">
@@ -20396,7 +21312,9 @@
         <f t="shared" si="18"/>
         <v>3200</v>
       </c>
-      <c r="M506" s="11"/>
+      <c r="M506" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="507" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A507" s="4" t="s">
@@ -20435,7 +21353,9 @@
         <f t="shared" si="18"/>
         <v>28000</v>
       </c>
-      <c r="M507" s="11"/>
+      <c r="M507" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="508" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A508" s="4" t="s">
@@ -20474,7 +21394,9 @@
         <f t="shared" si="18"/>
         <v>186178</v>
       </c>
-      <c r="M508" s="11"/>
+      <c r="M508" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="509" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A509" s="4" t="s">
@@ -20513,7 +21435,9 @@
         <f t="shared" si="18"/>
         <v>155620</v>
       </c>
-      <c r="M509" s="11"/>
+      <c r="M509" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="510" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A510" s="4" t="s">
@@ -20552,7 +21476,9 @@
         <f t="shared" si="18"/>
         <v>57366</v>
       </c>
-      <c r="M510" s="11"/>
+      <c r="M510" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="511" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A511" s="4" t="s">
@@ -20591,7 +21517,9 @@
         <f t="shared" si="18"/>
         <v>125468</v>
       </c>
-      <c r="M511" s="11"/>
+      <c r="M511" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="512" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A512" s="4" t="s">
@@ -20630,7 +21558,9 @@
         <f t="shared" si="18"/>
         <v>422850</v>
       </c>
-      <c r="M512" s="11"/>
+      <c r="M512" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="513" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A513" s="4" t="s">
@@ -20669,7 +21599,9 @@
         <f t="shared" si="18"/>
         <v>4100</v>
       </c>
-      <c r="M513" s="11"/>
+      <c r="M513" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="514" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A514" s="4" t="s">
@@ -20708,7 +21640,9 @@
         <f t="shared" si="18"/>
         <v>3500</v>
       </c>
-      <c r="M514" s="11"/>
+      <c r="M514" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="515" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A515" s="4" t="s">
@@ -20747,7 +21681,9 @@
         <f t="shared" si="18"/>
         <v>745417</v>
       </c>
-      <c r="M515" s="11"/>
+      <c r="M515" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="516" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A516" s="4" t="s">
@@ -20827,7 +21763,9 @@
         <f t="shared" si="18"/>
         <v>41445</v>
       </c>
-      <c r="M517" s="11"/>
+      <c r="M517" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="518" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A518" s="4" t="s">
@@ -20856,7 +21794,7 @@
       </c>
       <c r="I518" s="8"/>
       <c r="J518" s="9">
-        <f t="shared" ref="J518:J537" si="19">+H518+I518</f>
+        <f t="shared" ref="J518:J536" si="19">+H518+I518</f>
         <v>190000</v>
       </c>
       <c r="K518" s="8">
@@ -20866,7 +21804,9 @@
         <f t="shared" si="18"/>
         <v>20000</v>
       </c>
-      <c r="M518" s="11"/>
+      <c r="M518" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="519" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A519" s="4" t="s">
@@ -20905,7 +21845,9 @@
         <f t="shared" si="18"/>
         <v>7500</v>
       </c>
-      <c r="M519" s="11"/>
+      <c r="M519" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="520" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A520" s="4" t="s">
@@ -20944,7 +21886,9 @@
         <f t="shared" si="18"/>
         <v>90000</v>
       </c>
-      <c r="M520" s="11"/>
+      <c r="M520" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="521" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A521" s="4" t="s">
@@ -20983,7 +21927,9 @@
         <f t="shared" si="18"/>
         <v>8798</v>
       </c>
-      <c r="M521" s="11"/>
+      <c r="M521" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="522" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A522" s="4" t="s">
@@ -21022,7 +21968,9 @@
         <f t="shared" si="18"/>
         <v>11000</v>
       </c>
-      <c r="M522" s="11"/>
+      <c r="M522" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="523" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A523" s="4" t="s">
@@ -21102,7 +22050,9 @@
         <f t="shared" si="18"/>
         <v>85000</v>
       </c>
-      <c r="M524" s="11"/>
+      <c r="M524" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="525" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A525" s="4" t="s">
@@ -21141,7 +22091,9 @@
         <f t="shared" si="18"/>
         <v>5040</v>
       </c>
-      <c r="M525" s="11"/>
+      <c r="M525" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="526" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A526" s="4" t="s">
@@ -21180,7 +22132,9 @@
         <f t="shared" si="18"/>
         <v>159000</v>
       </c>
-      <c r="M526" s="11"/>
+      <c r="M526" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="527" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A527" s="4" t="s">
@@ -21219,7 +22173,9 @@
         <f t="shared" si="18"/>
         <v>53696</v>
       </c>
-      <c r="M527" s="11"/>
+      <c r="M527" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="528" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A528" s="4" t="s">
@@ -21260,7 +22216,9 @@
         <f t="shared" si="18"/>
         <v>-139392</v>
       </c>
-      <c r="M528" s="11"/>
+      <c r="M528" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="529" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A529" s="4" t="s">
@@ -21301,7 +22259,9 @@
         <f t="shared" si="18"/>
         <v>4043</v>
       </c>
-      <c r="M529" s="11"/>
+      <c r="M529" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="530" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A530" s="4" t="s">
@@ -21342,7 +22302,9 @@
         <f t="shared" si="18"/>
         <v>2143</v>
       </c>
-      <c r="M530" s="11"/>
+      <c r="M530" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="531" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A531" s="4" t="s">
@@ -21383,7 +22345,9 @@
         <f t="shared" si="18"/>
         <v>15771</v>
       </c>
-      <c r="M531" s="11"/>
+      <c r="M531" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="532" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A532" s="4" t="s">
@@ -21424,7 +22388,9 @@
         <f t="shared" si="18"/>
         <v>162460</v>
       </c>
-      <c r="M532" s="11"/>
+      <c r="M532" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="533" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A533" s="4" t="s">
@@ -21465,7 +22431,9 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="M533" s="11"/>
+      <c r="M533" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="534" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A534" s="4" t="s">
@@ -21506,7 +22474,9 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="M534" s="11"/>
+      <c r="M534" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="535" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A535" s="4" t="s">
@@ -21547,7 +22517,9 @@
         <f t="shared" si="18"/>
         <v>910</v>
       </c>
-      <c r="M535" s="11"/>
+      <c r="M535" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="536" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A536" s="4" t="s">
@@ -21588,7 +22560,9 @@
         <f t="shared" si="18"/>
         <v>600</v>
       </c>
-      <c r="M536" s="11"/>
+      <c r="M536" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="537" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A537" s="4" t="s">
@@ -21615,7 +22589,9 @@
       <c r="L537" s="8">
         <v>326202</v>
       </c>
-      <c r="M537" s="11"/>
+      <c r="M537" s="11">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
